--- a/information.xlsx
+++ b/information.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robschoen/Dropbox/CC/worldcup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{822E6CD9-2E97-2A4C-9950-6FEBFBEC1E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B9F0AB-E2E8-8847-B406-65FCB5427080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26080" yWindow="1780" windowWidth="27760" windowHeight="16680" activeTab="3" xr2:uid="{85689911-5AB9-B147-8B3A-3A9F276B987C}"/>
+    <workbookView xWindow="31320" yWindow="-21160" windowWidth="27760" windowHeight="16680" activeTab="1" xr2:uid="{85689911-5AB9-B147-8B3A-3A9F276B987C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rankings" sheetId="1" r:id="rId1"/>
-    <sheet name="Groups" sheetId="3" r:id="rId2"/>
-    <sheet name="Game Schedule" sheetId="2" r:id="rId3"/>
+    <sheet name="Actual Rankings" sheetId="1" r:id="rId1"/>
+    <sheet name="Actual Groups" sheetId="3" r:id="rId2"/>
+    <sheet name="Actual Schedule" sheetId="2" r:id="rId3"/>
     <sheet name="BSC Teams" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
